--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,69 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +759,14 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +800,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +841,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,43 +862,51 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +981,14 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1022,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,43 +1040,51 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1033,34 +1092,40 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-5900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1139,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1083,34 +1150,40 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1118,34 +1191,40 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-6700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1170,52 +1249,64 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1340,14 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1381,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1545,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1627,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1503,69 +1642,81 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1750,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,43 +1875,51 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1753,29 +1932,35 @@
       <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3300</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1809,8 +1994,14 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,43 +2035,55 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
       </c>
       <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>400</v>
+      </c>
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1888,34 +2091,40 @@
         <v>4400</v>
       </c>
       <c r="E46" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1949,23 +2158,29 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1975,17 +2190,23 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>200</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>200</v>
+      </c>
+      <c r="O48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2019,8 +2240,14 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,8 +2322,14 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2103,29 +2342,35 @@
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2404,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F54" s="3">
         <v>4400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>8000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,66 +2483,74 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1800</v>
       </c>
       <c r="J57" s="3">
         <v>1200</v>
       </c>
       <c r="K57" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="L57" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="M57" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -2294,78 +2561,96 @@
       <c r="M58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>1300</v>
       </c>
       <c r="F59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
-      </c>
-      <c r="F60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1800</v>
       </c>
       <c r="H60" s="3">
         <v>2100</v>
       </c>
       <c r="I60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2391,21 +2676,27 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>100</v>
+      </c>
+      <c r="O61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -2416,14 +2707,14 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2434,8 +2725,14 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2848,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1600</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1800</v>
       </c>
       <c r="H66" s="3">
         <v>2100</v>
       </c>
       <c r="I66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K66" s="3">
         <v>4300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +3070,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-29500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-27400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-31300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-28900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-27300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-26300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-24500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-21900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-18800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3234,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
         <v>2300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3316,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3424,10 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3047,14 +3444,14 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -3064,8 +3461,14 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3666,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2100</v>
-      </c>
       <c r="G89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2300</v>
       </c>
       <c r="K89" s="3">
         <v>-1600</v>
       </c>
       <c r="L89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,8 +3728,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3324,8 +3765,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,13 +3847,19 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -3409,28 +3868,34 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3909,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3946,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +4069,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E100" s="3">
-        <v>6900</v>
+        <v>3900</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +4151,51 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-2100</v>
-      </c>
       <c r="G102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H102" s="3">
+        <v>500</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,76 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +769,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -873,40 +887,43 @@
         <v>900</v>
       </c>
       <c r="E12" s="3">
+        <v>900</v>
+      </c>
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,49 +1068,53 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1400</v>
       </c>
       <c r="J17" s="3">
         <v>1400</v>
       </c>
       <c r="K17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,40 +1122,43 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1400</v>
       </c>
       <c r="J18" s="3">
         <v>-1400</v>
       </c>
       <c r="K18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1174,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1153,26 +1187,26 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1182,8 +1216,11 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1191,40 +1228,43 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1255,8 +1295,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1264,49 +1304,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1700,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1645,26 +1715,26 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1674,49 +1744,55 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1938,29 +2028,32 @@
       <c r="H42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3300</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2000,8 +2093,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,25 +2137,28 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
@@ -2068,63 +2167,69 @@
         <v>400</v>
       </c>
       <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
       </c>
       <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,26 +2269,29 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
       <c r="F48" s="3">
         <v>0</v>
       </c>
       <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2196,8 +2304,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>200</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
@@ -2205,8 +2313,11 @@
       <c r="O48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,25 +2445,28 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2355,13 +2475,13 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>200</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,54 +2615,58 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2543,8 +2677,8 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2553,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
@@ -2567,8 +2701,11 @@
       <c r="O58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2576,81 +2713,87 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>700</v>
       </c>
       <c r="O59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2682,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -2690,8 +2833,11 @@
       <c r="O61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2699,7 +2845,7 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -2707,8 +2853,8 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2716,8 +2862,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-33400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-27400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-28900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-27300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-21900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4000</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>2300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3624,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3450,11 +3649,11 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,16 +4080,19 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -3874,28 +4104,31 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,38 +4318,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>5900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>3400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -4116,8 +4362,11 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,8 +4406,11 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4166,36 +4418,39 @@
         <v>2300</v>
       </c>
       <c r="E102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,103 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -772,8 +776,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +823,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E12" s="3">
         <v>900</v>
       </c>
       <c r="F12" s="3">
+        <v>900</v>
+      </c>
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
+      <c r="K12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,31 +983,34 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2400</v>
-      </c>
       <c r="H17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1400</v>
       </c>
       <c r="K17" s="3">
         <v>1400</v>
       </c>
       <c r="L17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1400</v>
       </c>
       <c r="K18" s="3">
         <v>-1400</v>
       </c>
       <c r="L18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1208,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1190,26 +1224,26 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1219,52 +1253,58 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-2100</v>
       </c>
       <c r="E21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-6700</v>
-      </c>
       <c r="I21" s="3">
-        <v>-2100</v>
+        <v>-5800</v>
       </c>
       <c r="J21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1277,17 +1317,17 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1200</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1298,8 +1338,8 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1307,75 +1347,81 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1770,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1718,26 +1788,26 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -1747,52 +1817,58 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,119 +2050,126 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4800</v>
       </c>
-      <c r="I41" s="3">
-        <v>1700</v>
-      </c>
       <c r="J41" s="3">
+        <v>500</v>
+      </c>
+      <c r="K41" s="3">
         <v>3800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3300</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2096,31 +2189,34 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2140,119 +2236,128 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
       </c>
       <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="I46" s="3">
-        <v>2100</v>
-      </c>
       <c r="J46" s="3">
+        <v>700</v>
+      </c>
+      <c r="K46" s="3">
         <v>4200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2272,8 +2377,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2281,22 +2389,22 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -2307,8 +2415,8 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>200</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
@@ -2316,8 +2424,11 @@
       <c r="P48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,28 +2565,31 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -2478,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>200</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5600</v>
       </c>
-      <c r="I54" s="3">
-        <v>2100</v>
-      </c>
       <c r="J54" s="3">
+        <v>800</v>
+      </c>
+      <c r="K54" s="3">
         <v>4200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2746,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O57" s="3">
+        <v>900</v>
+      </c>
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
-        <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2684,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
@@ -2704,107 +2838,116 @@
       <c r="P58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1000</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>900</v>
+      </c>
+      <c r="M59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>700</v>
       </c>
       <c r="P59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L60" s="3">
         <v>2100</v>
       </c>
-      <c r="J60" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2828,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
@@ -2836,25 +2979,28 @@
       <c r="P61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2865,8 +3011,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L66" s="3">
         <v>2100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="K66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>4300</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-35700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-33400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-27400</v>
       </c>
-      <c r="I72" s="3">
-        <v>-31300</v>
-      </c>
       <c r="J72" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-28900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-21900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K76" s="3">
         <v>2300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3652,11 +3851,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,19 +4171,20 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3974,8 +4195,8 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3995,8 +4216,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4310,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4094,8 +4324,8 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -4106,29 +4336,32 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,31 +4378,32 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,41 +4564,44 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3900</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>3400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -4365,31 +4611,34 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2300</v>
+        <v>-1600</v>
       </c>
       <c r="E102" s="3">
         <v>2300</v>
       </c>
       <c r="F102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,84 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,8 +761,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -779,8 +782,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +832,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>900</v>
       </c>
       <c r="F12" s="3">
         <v>900</v>
       </c>
       <c r="G12" s="3">
+        <v>900</v>
+      </c>
+      <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="L12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1012,8 +1031,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1033,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1400</v>
       </c>
       <c r="L17" s="3">
         <v>1400</v>
       </c>
       <c r="M17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1400</v>
       </c>
       <c r="L18" s="3">
         <v>-1400</v>
       </c>
       <c r="M18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,16 +1241,17 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1230,23 +1263,23 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1256,55 +1289,61 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1317,21 +1356,21 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1341,8 +1380,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1350,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1423,8 +1468,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1444,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,16 +1839,19 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1794,23 +1863,23 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -1820,55 +1889,61 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,55 +2136,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2128,25 +2217,28 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2171,8 +2263,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2192,8 +2284,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2218,8 +2313,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2239,8 +2334,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2265,76 +2363,82 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>400</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>600</v>
       </c>
       <c r="O45" s="3">
         <v>600</v>
       </c>
       <c r="P45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2359,8 +2463,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2380,8 +2484,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2392,22 +2499,22 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
+      <c r="K48" s="3">
+        <v>100</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
@@ -2418,8 +2525,8 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>200</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
@@ -2427,8 +2534,11 @@
       <c r="Q48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2591,8 +2710,8 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2601,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>200</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -2615,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,55 +2876,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2818,16 +2951,16 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -2841,8 +2974,11 @@
       <c r="Q58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2852,8 +2988,8 @@
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
@@ -2862,81 +2998,87 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>700</v>
       </c>
       <c r="Q59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2950,7 +3092,7 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2974,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -2982,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3014,8 +3159,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3029,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-37800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-35700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-31500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-27400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-20600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-28900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3854,11 +4052,11 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -3871,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4186,8 +4406,8 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4195,11 +4415,11 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4219,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4539,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4327,8 +4556,8 @@
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -4336,32 +4565,35 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4405,8 +4638,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4426,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,44 +4809,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>5900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>3400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -4614,8 +4859,11 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4640,8 +4888,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4661,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
-      </c>
-      <c r="E102" s="3">
-        <v>2300</v>
       </c>
       <c r="F102" s="3">
         <v>2300</v>
       </c>
       <c r="G102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -764,8 +768,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -785,8 +789,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,8 +842,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>900</v>
       </c>
       <c r="G12" s="3">
         <v>900</v>
       </c>
       <c r="H12" s="3">
+        <v>900</v>
+      </c>
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1034,8 +1054,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1400</v>
       </c>
       <c r="M17" s="3">
         <v>1400</v>
       </c>
       <c r="N17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1400</v>
       </c>
       <c r="M18" s="3">
         <v>-1400</v>
       </c>
       <c r="N18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,19 +1275,20 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1266,23 +1300,23 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1292,58 +1326,64 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1359,21 +1399,21 @@
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1383,8 +1423,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1471,8 +1517,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,19 +1909,22 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -1866,23 +1936,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -1892,58 +1962,64 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2220,25 +2310,28 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3300</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2266,8 +2359,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2287,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2316,8 +2412,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2366,79 +2465,85 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>400</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
+        <v>400</v>
+      </c>
+      <c r="O45" s="3">
         <v>900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>600</v>
       </c>
       <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2466,8 +2571,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2487,8 +2592,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2502,22 +2610,22 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
+      <c r="L48" s="3">
+        <v>100</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
@@ -2528,8 +2636,8 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>200</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
@@ -2537,8 +2645,11 @@
       <c r="R48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2713,8 +2833,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2723,13 +2843,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
+      <c r="P52" s="3">
+        <v>200</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,63 +3007,67 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2954,16 +3088,16 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
@@ -2977,8 +3111,11 @@
       <c r="R58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2991,8 +3128,8 @@
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -3001,84 +3138,90 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>700</v>
       </c>
       <c r="R59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3095,7 +3238,7 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -3119,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -3127,8 +3270,11 @@
       <c r="R61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3162,8 +3308,8 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-37800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-35700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-29500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-27400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-20600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-28900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-24500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4055,11 +4254,11 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4409,8 +4630,8 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -4418,11 +4639,11 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4559,8 +4789,8 @@
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -4568,32 +4798,35 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4641,8 +4875,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,47 +5055,50 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>5900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>3400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -4862,8 +5108,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4891,8 +5140,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
-      </c>
-      <c r="F102" s="3">
-        <v>2300</v>
       </c>
       <c r="G102" s="3">
         <v>2300</v>
       </c>
       <c r="H102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,91 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,8 +775,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -792,8 +796,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -845,8 +852,11 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -898,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>900</v>
       </c>
       <c r="H12" s="3">
         <v>900</v>
       </c>
       <c r="I12" s="3">
+        <v>900</v>
+      </c>
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1057,8 +1077,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1400</v>
       </c>
       <c r="N17" s="3">
         <v>1400</v>
       </c>
       <c r="O17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1400</v>
       </c>
       <c r="N18" s="3">
         <v>-1400</v>
       </c>
       <c r="O18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,22 +1309,23 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1303,23 +1337,23 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1329,61 +1363,67 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1402,21 +1442,21 @@
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1426,8 +1466,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1435,61 +1475,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1520,8 +1566,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1541,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,22 +1979,25 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1939,23 +2009,23 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -1965,61 +2035,67 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2313,25 +2403,28 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3300</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2362,8 +2455,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2383,8 +2476,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2415,8 +2511,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2436,8 +2532,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2468,82 +2567,88 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>400</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
       </c>
       <c r="O45" s="3">
+        <v>400</v>
+      </c>
+      <c r="P45" s="3">
         <v>900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
       </c>
       <c r="R45" s="3">
+        <v>600</v>
+      </c>
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2574,8 +2679,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2595,8 +2700,11 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2613,22 +2721,22 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
+        <v>100</v>
+      </c>
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
+      <c r="M48" s="3">
+        <v>100</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
@@ -2639,8 +2747,8 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>200</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
@@ -2648,8 +2756,11 @@
       <c r="S48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,8 +2924,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2836,8 +2956,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2846,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>200</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,61 +3138,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3070,7 +3204,7 @@
         <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3091,16 +3225,16 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>2400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
@@ -3114,8 +3248,11 @@
       <c r="S58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3131,8 +3268,8 @@
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -3141,92 +3278,98 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>700</v>
       </c>
       <c r="S59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -3241,7 +3384,7 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3265,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -3273,8 +3416,11 @@
       <c r="S61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3311,8 +3457,8 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-37800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-35700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-28900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-21900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4257,11 +4456,11 @@
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4633,8 +4854,8 @@
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4642,11 +4863,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +4999,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4792,8 +5022,8 @@
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -4801,32 +5031,35 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3300</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4878,8 +5112,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,50 +5301,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3900</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>5900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -5111,8 +5357,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5143,8 +5392,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2300</v>
       </c>
       <c r="H102" s="3">
         <v>2300</v>
       </c>
       <c r="I102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,99 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,8 +788,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -806,8 +809,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +871,11 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
-        <v>800</v>
-      </c>
       <c r="H12" s="3">
+        <v>900</v>
+      </c>
+      <c r="I12" s="3">
         <v>1100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>900</v>
       </c>
       <c r="J12" s="3">
         <v>900</v>
       </c>
       <c r="K12" s="3">
+        <v>900</v>
+      </c>
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1081,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1103,8 +1122,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1124,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1400</v>
       </c>
       <c r="P17" s="3">
         <v>1400</v>
       </c>
       <c r="Q17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1400</v>
       </c>
       <c r="P18" s="3">
         <v>-1400</v>
       </c>
       <c r="Q18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1376,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1358,14 +1391,14 @@
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1377,23 +1410,23 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1403,67 +1436,73 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1488,21 +1527,21 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1512,8 +1551,8 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1521,67 +1560,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1618,8 +1663,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1639,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2118,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2066,14 +2135,14 @@
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2085,23 +2154,23 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2111,67 +2180,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>4100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2499,25 +2588,28 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3300</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2554,8 +2646,8 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2575,8 +2667,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2613,8 +2708,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2634,8 +2729,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2672,88 +2770,94 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>400</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
       </c>
       <c r="Q45" s="3">
+        <v>400</v>
+      </c>
+      <c r="R45" s="3">
         <v>900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
       </c>
       <c r="T45" s="3">
+        <v>600</v>
+      </c>
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2790,8 +2894,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2811,8 +2915,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2835,22 +2942,22 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
+        <v>100</v>
+      </c>
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>100</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -2861,8 +2968,8 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>200</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>200</v>
@@ -2870,8 +2977,11 @@
       <c r="U48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3082,8 +3201,8 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3092,13 +3211,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="S52" s="3">
+        <v>200</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,67 +3399,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="E57" s="3">
         <v>1300</v>
       </c>
       <c r="F57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3344,7 +3477,7 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3365,16 +3498,16 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>2400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
@@ -3388,8 +3521,11 @@
       <c r="U58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3411,8 +3547,8 @@
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3421,93 +3557,99 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>700</v>
       </c>
       <c r="U59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3518,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
@@ -3533,7 +3675,7 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3557,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -3565,8 +3707,11 @@
       <c r="U61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3609,8 +3754,8 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-49000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-37800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-35700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-26300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-24500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-21900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-18800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-3200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4661,11 +4859,11 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,13 +5274,14 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>4</v>
@@ -5081,8 +5301,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5090,11 +5310,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -5114,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,13 +5458,16 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -5258,8 +5487,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -5267,32 +5496,35 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5352,8 +5585,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,56 +5792,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>5900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>3400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5854,11 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5647,8 +5895,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5668,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
-      </c>
-      <c r="I102" s="3">
-        <v>2300</v>
       </c>
       <c r="J102" s="3">
         <v>2300</v>
       </c>
       <c r="K102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>GRI</t>
   </si>
@@ -656,102 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -791,8 +795,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -812,8 +816,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>900</v>
       </c>
       <c r="K12" s="3">
         <v>900</v>
       </c>
       <c r="L12" s="3">
+        <v>900</v>
+      </c>
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1125,8 +1145,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1400</v>
       </c>
       <c r="Q17" s="3">
         <v>1400</v>
       </c>
       <c r="R17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-1400</v>
       </c>
       <c r="Q18" s="3">
         <v>-1400</v>
       </c>
       <c r="R18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1394,14 +1428,14 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1413,23 +1447,23 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1439,70 +1473,76 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1530,21 +1570,21 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1554,8 +1594,8 @@
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1563,70 +1603,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1666,8 +1712,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2138,14 +2208,14 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2157,23 +2227,23 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2183,70 +2253,76 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2591,25 +2681,28 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3300</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2649,8 +2742,8 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2670,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2711,8 +2807,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2732,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2773,91 +2872,97 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>400</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>400</v>
       </c>
       <c r="R45" s="3">
+        <v>400</v>
+      </c>
+      <c r="S45" s="3">
         <v>900</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
       <c r="U45" s="3">
+        <v>600</v>
+      </c>
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E46" s="3">
         <v>8600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2897,8 +3002,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2918,8 +3023,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2945,22 +3053,22 @@
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>100</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -2971,8 +3079,8 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>200</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>200</v>
@@ -2980,8 +3088,11 @@
       <c r="V48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3204,8 +3324,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3214,13 +3334,13 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
+      <c r="T52" s="3">
+        <v>200</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1300</v>
       </c>
       <c r="F57" s="3">
         <v>1300</v>
       </c>
       <c r="G57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3480,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -3501,16 +3635,16 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>2400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
@@ -3524,8 +3658,11 @@
       <c r="V58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3550,8 +3687,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3560,96 +3697,102 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>700</v>
       </c>
       <c r="V59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3663,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -3678,7 +3821,7 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3702,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>100</v>
@@ -3710,8 +3853,11 @@
       <c r="V61" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3757,8 +3903,8 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-49000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-37800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-35700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-33400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-26300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-24500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-21900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-18800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E76" s="3">
         <v>6000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4862,11 +5061,11 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,16 +5495,17 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
@@ -5304,8 +5525,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5313,11 +5534,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,16 +5688,19 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
@@ -5490,8 +5720,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -5499,32 +5729,35 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3300</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5588,8 +5822,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,59 +6038,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E100" s="3">
         <v>7100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>5900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>3400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5898,8 +6147,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>2300</v>
       </c>
       <c r="K102" s="3">
         <v>2300</v>
       </c>
       <c r="L102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
     </row>
